--- a/ev_data/titles.xlsx
+++ b/ev_data/titles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Documents\Projects\manuscript_reviews\ev_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEE56ED-5126-4E26-A7CB-CD4ABE2C4BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D8F2C2-54FF-45B2-9341-304CFBDB35BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15000" yWindow="0" windowWidth="13875" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,18 +66,12 @@
     <t>sample_2b_filtered.npy</t>
   </si>
   <si>
-    <t>Exponential 2</t>
-  </si>
-  <si>
     <t>sample_13a_filtered.npy</t>
   </si>
   <si>
     <t>sample_13b_filtered.npy</t>
   </si>
   <si>
-    <t>Reg-Arrest A</t>
-  </si>
-  <si>
     <t>Dis-Arrest 4A</t>
   </si>
   <si>
@@ -90,9 +84,6 @@
     <t>sample_15b_filtered.npy</t>
   </si>
   <si>
-    <t>Reg-Arrest B</t>
-  </si>
-  <si>
     <t>SHX_biorep2A.npy</t>
   </si>
   <si>
@@ -142,6 +133,15 @@
   </si>
   <si>
     <t>d</t>
+  </si>
+  <si>
+    <t>Reg-Arrest 1</t>
+  </si>
+  <si>
+    <t>Reg-Arrest 2A</t>
+  </si>
+  <si>
+    <t>Reg-Arrest 2B</t>
   </si>
 </sst>
 </file>
@@ -526,7 +526,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -534,10 +534,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -545,10 +545,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -556,10 +556,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -567,10 +567,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -578,10 +578,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -589,79 +589,79 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
